--- a/data/trans_dic/P64D$andando_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P64D$andando_2023-Edad-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, se desplaza desde su casa al centro de trabajo/estudios andando</t>
+          <t>Población que, al menos, se desplaza desde su casa al centro de trabajo/estudios andando (tasa de respuesta: 99,46%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>16,07; 47,04</t>
+          <t>16,07; 46,87</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>20,23; 46,47</t>
+          <t>20,9; 46,99</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>21,86; 42,95</t>
+          <t>21,74; 41,63</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>15,7; 26,2</t>
+          <t>15,84; 26,3</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>14,64; 37,28</t>
+          <t>14,5; 37,49</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17,2; 28,75</t>
+          <t>16,98; 28,57</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>17,32; 24,92</t>
+          <t>17,05; 24,35</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>30,12; 38,37</t>
+          <t>30,42; 38,46</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>23,73; 29,42</t>
+          <t>23,73; 29,28</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,23; 21,71</t>
+          <t>5,09; 21,38</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>25,51; 37,05</t>
+          <t>25,49; 37,09</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11,25; 27,02</t>
+          <t>10,02; 27,13</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>21,74; 31,26</t>
+          <t>22,33; 31,97</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>41,19; 50,99</t>
+          <t>40,19; 50,54</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>31,04; 38,15</t>
+          <t>30,82; 37,97</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>31,95; 75,12</t>
+          <t>32,65; 71,44</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>44,31; 76,8</t>
+          <t>44,5; 75,86</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>43,34; 68,32</t>
+          <t>44,13; 68,97</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>13,03; 23,09</t>
+          <t>13,01; 22,96</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>28,65; 37,39</t>
+          <t>28,98; 37,06</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>19,74; 28,52</t>
+          <t>20,19; 28,52</t>
         </is>
       </c>
     </row>
@@ -978,7 +978,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, se desplaza desde su casa al centro de trabajo/estudios andando</t>
+          <t>Población que, al menos, se desplaza desde su casa al centro de trabajo/estudios andando (tasa de respuesta: 99,46%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1083,17 +1083,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>14562; 42629</t>
+          <t>14560; 42473</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>16436; 37752</t>
+          <t>16979; 38177</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>37562; 73807</t>
+          <t>37357; 71548</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>55020; 91793</t>
+          <t>55509; 92152</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>51191; 130388</t>
+          <t>50695; 131095</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>120399; 201269</t>
+          <t>118887; 200015</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>80032; 115113</t>
+          <t>78743; 112482</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>105786; 134763</t>
+          <t>106854; 135065</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>192955; 239231</t>
+          <t>192941; 238101</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>38989; 161779</t>
+          <t>37905; 159310</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>115534; 167784</t>
+          <t>115440; 167996</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>134831; 323747</t>
+          <t>119995; 324980</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>65020; 93512</t>
+          <t>66792; 95620</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>85732; 106131</t>
+          <t>83650; 105197</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>157460; 193502</t>
+          <t>156354; 192625</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>5413; 12727</t>
+          <t>5532; 12104</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>7866; 13633</t>
+          <t>7899; 13466</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>15037; 23702</t>
+          <t>15310; 23930</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>256105; 453789</t>
+          <t>255714; 451392</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>418556; 546259</t>
+          <t>423386; 541374</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>676360; 977176</t>
+          <t>691675; 977130</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P64D$andando_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P64D$andando_2023-Edad-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>34,99%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>32,18%</t>
+          <t>33,36%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
+          <t>34,23%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>16,07; 46,87</t>
+          <t>21,15; 50,28</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>20,9; 46,99</t>
+          <t>21,87; 46,63</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>21,74; 41,63</t>
+          <t>24,68; 44,8</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>28,31%</t>
+          <t>36,19%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>27,44%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>15,84; 26,3</t>
+          <t>15,7; 26,29</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>14,5; 37,49</t>
+          <t>30,92; 41,57</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16,98; 28,57</t>
+          <t>23,4; 30,91</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>34,11%</t>
+          <t>34,97%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>27,05%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>17,05; 24,35</t>
+          <t>17,63; 25,15</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>30,42; 38,46</t>
+          <t>30,96; 39,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>23,73; 29,28</t>
+          <t>24,43; 29,93</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>32,44%</t>
+          <t>34,09%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>26,81%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,09; 21,38</t>
+          <t>17,55; 24,64</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>25,49; 37,09</t>
+          <t>30,63; 37,66</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10,02; 27,13</t>
+          <t>24,33; 29,44</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>45,76%</t>
+          <t>45,17%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>34,43%</t>
+          <t>33,87%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>22,33; 31,97</t>
+          <t>21,25; 30,7</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>40,19; 50,54</t>
+          <t>40,22; 50,25</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>30,82; 37,97</t>
+          <t>30,36; 37,63</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>51,67%</t>
+          <t>50,83%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>60,88%</t>
+          <t>57,0%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>56,38%</t>
+          <t>53,95%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>32,65; 71,44</t>
+          <t>32,13; 70,79</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>44,5; 75,86</t>
+          <t>40,1; 72,15</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>44,13; 68,97</t>
+          <t>40,84; 66,63</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>53,32%</t>
+          <t>51,19%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>53,32%</t>
+          <t>51,19%</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>34,08%</t>
+          <t>36,72%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>28,9%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>13,01; 22,96</t>
+          <t>20,65; 24,9</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>28,98; 37,06</t>
+          <t>34,48; 38,88</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>20,19; 28,52</t>
+          <t>27,34; 30,33</t>
         </is>
       </c>
     </row>
@@ -1060,17 +1060,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>27341</t>
+          <t>36675</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>26142</t>
+          <t>30602</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>53483</t>
+          <t>67277</t>
         </is>
       </c>
     </row>
@@ -1083,17 +1083,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>14560; 42473</t>
+          <t>22170; 52700</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>16979; 38177</t>
+          <t>20065; 42780</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>37357; 71548</t>
+          <t>48510; 88059</t>
         </is>
       </c>
     </row>
@@ -1133,17 +1133,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>70604</t>
+          <t>81078</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>99018</t>
+          <t>114031</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>169622</t>
+          <t>195109</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>55509; 92152</t>
+          <t>62150; 104101</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>50695; 131095</t>
+          <t>97448; 131006</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>118887; 200015</t>
+          <t>166351; 219780</t>
         </is>
       </c>
     </row>
@@ -1206,17 +1206,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>94952</t>
+          <t>113677</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>119812</t>
+          <t>138826</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>214764</t>
+          <t>252503</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>78743; 112482</t>
+          <t>94611; 134922</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>106854; 135065</t>
+          <t>122907; 154826</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>192941; 238101</t>
+          <t>228056; 279422</t>
         </is>
       </c>
     </row>
@@ -1279,17 +1279,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>102125</t>
+          <t>112614</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>146907</t>
+          <t>155096</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>249031</t>
+          <t>267710</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>37905; 159310</t>
+          <t>95405; 133915</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>115440; 167996</t>
+          <t>139350; 171343</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>119995; 324980</t>
+          <t>242945; 293983</t>
         </is>
       </c>
     </row>
@@ -1352,17 +1352,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>79386</t>
+          <t>84611</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>95243</t>
+          <t>105135</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>174629</t>
+          <t>189746</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>66792; 95620</t>
+          <t>69580; 100522</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>83650; 105197</t>
+          <t>93610; 116943</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>156354; 192625</t>
+          <t>170084; 210753</t>
         </is>
       </c>
     </row>
@@ -1425,17 +1425,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>8754</t>
+          <t>9741</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>10806</t>
+          <t>11239</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>19560</t>
+          <t>20981</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>5532; 12104</t>
+          <t>6158; 13567</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>7899; 13466</t>
+          <t>7908; 14229</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>15310; 23930</t>
+          <t>15882; 25910</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>852</t>
+          <t>930</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>852</t>
+          <t>930</t>
         </is>
       </c>
     </row>
@@ -1521,7 +1521,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 1598</t>
+          <t>0; 1817</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 1598</t>
+          <t>0; 1817</t>
         </is>
       </c>
     </row>
@@ -1571,17 +1571,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>384014</t>
+          <t>439326</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>497928</t>
+          <t>554929</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>881942</t>
+          <t>994255</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>255714; 451392</t>
+          <t>398335; 480334</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>423386; 541374</t>
+          <t>521053; 587603</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>691675; 977130</t>
+          <t>940498; 1043525</t>
         </is>
       </c>
     </row>
